--- a/output/13_대성단가_검토요약.xlsx
+++ b/output/13_대성단가_검토요약.xlsx
@@ -697,7 +697,7 @@
         <v>40476180</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>55941700</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>47710885.87799999</v>
+        <v>47680619.87799999</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>73770040</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>55704470.07800001</v>
+        <v>55681097.27800001</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>100727780</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>65924718.83999998</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>40476180</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>6</v>
@@ -879,7 +879,7 @@
         <v>56118320</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>47709791.64199999</v>
+        <v>47679525.64199999</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6</v>
@@ -917,7 +917,7 @@
         <v>74123280</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55702281.60600001</v>
+        <v>55678908.80600001</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>101081020</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>65922530.36799998</v>
+        <v>65870388.76799998</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>75626915.888</v>
+        <v>75596051.888</v>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>83890988.12600002</v>
+        <v>83816970.92600001</v>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>23</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>91513678.52200001</v>
+        <v>91475323.32200001</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>103910327.142</v>
+        <v>103814434.342</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>75623633.18000001</v>
+        <v>75592769.18000001</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>83887705.41800003</v>
+        <v>83813688.21800002</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>91509301.57800001</v>
+        <v>91470946.37800001</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>27</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>103905950.198</v>
+        <v>103810057.398</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
